--- a/Data/Cleaned_Dataset.xlsx
+++ b/Data/Cleaned_Dataset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LuxDev\Jumia-Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E538815C-3217-4845-84B6-217C5D5CB130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{182119DD-C33C-40F7-92AA-C3C83AF0BDFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="0" windowWidth="18960" windowHeight="10905" xr2:uid="{F724BAED-E21B-4959-AB5C-7DEDF7868D06}"/>
+    <workbookView xWindow="1875" yWindow="345" windowWidth="18960" windowHeight="10905" activeTab="1" xr2:uid="{F724BAED-E21B-4959-AB5C-7DEDF7868D06}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="11" r:id="rId1"/>
@@ -31,15 +31,15 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId9"/>
-    <pivotCache cacheId="13" r:id="rId10"/>
-    <pivotCache cacheId="16" r:id="rId11"/>
+    <pivotCache cacheId="3" r:id="rId9"/>
+    <pivotCache cacheId="4" r:id="rId10"/>
+    <pivotCache cacheId="5" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
       <x14:pivotCaches>
-        <pivotCache cacheId="3" r:id="rId12"/>
-        <pivotCache cacheId="4" r:id="rId13"/>
+        <pivotCache cacheId="6" r:id="rId12"/>
+        <pivotCache cacheId="7" r:id="rId13"/>
       </x14:pivotCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -1731,7 +1731,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1750,7 +1750,6 @@
     </xf>
     <xf numFmtId="1" fontId="13" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
@@ -3453,6 +3452,22 @@
           <a:effectLst/>
         </c:spPr>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent4">
+              <a:tint val="65000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -3532,6 +3547,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-90B2-4D78-96F9-96E16CFFE8AB}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -19738,7 +19758,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6BD31B8F-D226-4596-A6AF-29E4537AA15B}" name="PivotTable15" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6BD31B8F-D226-4596-A6AF-29E4537AA15B}" name="PivotTable15" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A117:C134" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -19794,7 +19814,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5CD1A830-31BA-4817-81C3-6CE0AA259A33}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5CD1A830-31BA-4817-81C3-6CE0AA259A33}" name="PivotTable8" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O11:Q28" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -19850,7 +19870,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EFDAD4E4-C26C-496B-A11A-9EE9724E92AD}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EFDAD4E4-C26C-496B-A11A-9EE9724E92AD}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
@@ -20101,7 +20121,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D9D92604-793B-4319-A370-7DC4E2A2C49D}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D9D92604-793B-4319-A370-7DC4E2A2C49D}" name="PivotTable2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="A3:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
@@ -20352,7 +20372,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DA905DFB-C973-4C9C-840B-E78AFF53839D}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DA905DFB-C973-4C9C-840B-E78AFF53839D}" name="PivotTable3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField axis="axisRow" showAll="0" measureFilter="1" sortType="descending">
@@ -20583,7 +20603,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EFAE31FC-E6B6-4D9B-9A33-D3EF8381E0AE}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EFAE31FC-E6B6-4D9B-9A33-D3EF8381E0AE}" name="PivotTable4" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0">
@@ -20959,7 +20979,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{26585855-249A-47F4-BA3A-7E7FAFB36FB9}" name="PivotTable10" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{26585855-249A-47F4-BA3A-7E7FAFB36FB9}" name="PivotTable10" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -20995,7 +21015,7 @@
   <dataFields count="1">
     <dataField name="Count of Product" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="7">
+  <chartFormats count="8">
     <chartFormat chart="1" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -21074,6 +21094,18 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="1" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotHierarchies count="17">
     <pivotHierarchy dragToData="1"/>
@@ -21123,7 +21155,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E42A09EC-F2E1-4B20-8A1D-D2C35474CD9D}" name="PivotTable18" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E42A09EC-F2E1-4B20-8A1D-D2C35474CD9D}" name="PivotTable18" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -21630,7 +21662,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="17"/>
+    <col min="1" max="16384" width="9.140625" style="16"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -27166,62 +27198,64 @@
         <v>Average</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="3"/>
       <c r="B117" s="4"/>
       <c r="C117" s="5"/>
+      <c r="D117" s="5"/>
+      <c r="E117" s="5"/>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="6"/>
       <c r="B118" s="7"/>
       <c r="C118" s="8"/>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="6"/>
       <c r="B119" s="7"/>
       <c r="C119" s="8"/>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="6"/>
       <c r="B120" s="7"/>
       <c r="C120" s="8"/>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="6"/>
       <c r="B121" s="7"/>
       <c r="C121" s="8"/>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="6"/>
       <c r="B122" s="7"/>
       <c r="C122" s="8"/>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="6"/>
       <c r="B123" s="7"/>
       <c r="C123" s="8"/>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="6"/>
       <c r="B124" s="7"/>
       <c r="C124" s="8"/>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="6"/>
       <c r="B125" s="7"/>
       <c r="C125" s="8"/>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="6"/>
       <c r="B126" s="7"/>
       <c r="C126" s="8"/>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="6"/>
       <c r="B127" s="7"/>
       <c r="C127" s="8"/>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="6"/>
       <c r="B128" s="7"/>
       <c r="C128" s="8"/>
@@ -27684,7 +27718,7 @@
       <c r="A4" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4">
         <v>58</v>
       </c>
     </row>
@@ -27692,7 +27726,7 @@
       <c r="A5" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5">
         <v>18</v>
       </c>
     </row>
@@ -27700,7 +27734,7 @@
       <c r="A6" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6">
         <v>32</v>
       </c>
     </row>
@@ -27708,7 +27742,7 @@
       <c r="A7" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7">
         <v>108</v>
       </c>
     </row>
